--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>Record</t>
   </si>
@@ -30,133 +30,145 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Little Bill</t>
+  </si>
+  <si>
     <t>Pho_King</t>
   </si>
   <si>
-    <t>Little Bill</t>
-  </si>
-  <si>
     <t>Philadelphia Bills Mafia</t>
   </si>
   <si>
+    <t>19th St Halal Cart</t>
+  </si>
+  <si>
+    <t>The Golden Receivers</t>
+  </si>
+  <si>
+    <t>Eli</t>
+  </si>
+  <si>
+    <t>Cman</t>
+  </si>
+  <si>
     <t>J. Dobbs Holdings LLC</t>
   </si>
   <si>
-    <t>19th St Halal Cart</t>
-  </si>
-  <si>
-    <t>The Golden Receivers</t>
-  </si>
-  <si>
     <t>Lets Get Structural</t>
   </si>
   <si>
     <t>Tomas</t>
   </si>
   <si>
-    <t>Cman</t>
+    <t>Daddy's Finally Home</t>
   </si>
   <si>
     <t>Prahlad's Ghost</t>
   </si>
   <si>
-    <t>Eli</t>
-  </si>
-  <si>
-    <t>Daddy's Finally Home</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>99.3%</t>
-  </si>
-  <si>
-    <t>89.5%</t>
-  </si>
-  <si>
-    <t>88.6%</t>
-  </si>
-  <si>
-    <t>68.9%</t>
-  </si>
-  <si>
-    <t>49.1%</t>
-  </si>
-  <si>
-    <t>47.7%</t>
-  </si>
-  <si>
-    <t>40.9%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-14186</t>
-  </si>
-  <si>
-    <t>-852</t>
-  </si>
-  <si>
-    <t>-777</t>
-  </si>
-  <si>
-    <t>-222</t>
-  </si>
-  <si>
-    <t>+104</t>
-  </si>
-  <si>
-    <t>+110</t>
-  </si>
-  <si>
-    <t>+144</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>94.4%</t>
+  </si>
+  <si>
+    <t>93.5%</t>
+  </si>
+  <si>
+    <t>83.8%</t>
+  </si>
+  <si>
+    <t>69.3%</t>
+  </si>
+  <si>
+    <t>30.7%</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-1941</t>
+  </si>
+  <si>
+    <t>-1686</t>
+  </si>
+  <si>
+    <t>-1438</t>
+  </si>
+  <si>
+    <t>-517</t>
+  </si>
+  <si>
+    <t>-226</t>
+  </si>
+  <si>
+    <t>+226</t>
+  </si>
+  <si>
+    <t>+378</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>+2400</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>70.9%</t>
-  </si>
-  <si>
-    <t>20.6%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>63.5%</t>
+  </si>
+  <si>
+    <t>20.8%</t>
+  </si>
+  <si>
+    <t>7.3%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -165,58 +177,52 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-244</t>
-  </si>
-  <si>
-    <t>+385</t>
-  </si>
-  <si>
-    <t>+1329</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-174</t>
+  </si>
+  <si>
+    <t>+381</t>
+  </si>
+  <si>
+    <t>+1270</t>
+  </si>
+  <si>
+    <t>+2532</t>
+  </si>
+  <si>
+    <t>+4445</t>
+  </si>
+  <si>
+    <t>+5782</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>70.6%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
+    <t>56.2%</t>
+  </si>
+  <si>
+    <t>25.3%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-240</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1752</t>
-  </si>
-  <si>
-    <t>+3126</t>
+    <t>-128</t>
+  </si>
+  <si>
+    <t>+295</t>
+  </si>
+  <si>
+    <t>+706</t>
+  </si>
+  <si>
+    <t>+2757</t>
   </si>
   <si>
     <t>+33233</t>
@@ -602,10 +608,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -613,13 +619,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,10 +636,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,10 +650,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -655,13 +661,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -669,13 +675,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -683,13 +689,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -697,13 +703,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -711,13 +717,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -725,13 +731,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -739,13 +745,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -756,10 +762,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -780,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -788,44 +794,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -833,13 +839,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -850,10 +856,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -861,13 +867,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -875,83 +881,83 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -986,10 +992,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -997,13 +1003,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1011,13 +1017,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1025,41 +1031,41 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1067,69 +1073,69 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1140,10 +1146,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
   <si>
     <t>Record</t>
   </si>
@@ -39,193 +39,202 @@
     <t>Philadelphia Bills Mafia</t>
   </si>
   <si>
+    <t>Eli</t>
+  </si>
+  <si>
     <t>19th St Halal Cart</t>
   </si>
   <si>
     <t>The Golden Receivers</t>
   </si>
   <si>
-    <t>Eli</t>
+    <t>Lets Get Structural</t>
+  </si>
+  <si>
+    <t>J. Dobbs Holdings LLC</t>
+  </si>
+  <si>
+    <t>Daddy's Finally Home</t>
   </si>
   <si>
     <t>Cman</t>
   </si>
   <si>
-    <t>J. Dobbs Holdings LLC</t>
-  </si>
-  <si>
-    <t>Lets Get Structural</t>
-  </si>
-  <si>
     <t>Tomas</t>
   </si>
   <si>
-    <t>Daddy's Finally Home</t>
-  </si>
-  <si>
     <t>Prahlad's Ghost</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>95.1%</t>
-  </si>
-  <si>
-    <t>94.4%</t>
-  </si>
-  <si>
-    <t>93.5%</t>
-  </si>
-  <si>
-    <t>83.8%</t>
-  </si>
-  <si>
-    <t>69.3%</t>
-  </si>
-  <si>
-    <t>30.7%</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>87.9%</t>
+  </si>
+  <si>
+    <t>80.2%</t>
+  </si>
+  <si>
+    <t>73.0%</t>
+  </si>
+  <si>
+    <t>68.7%</t>
+  </si>
+  <si>
+    <t>64.9%</t>
+  </si>
+  <si>
+    <t>64.3%</t>
+  </si>
+  <si>
+    <t>36.1%</t>
+  </si>
+  <si>
+    <t>25.0%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-726</t>
+  </si>
+  <si>
+    <t>-405</t>
+  </si>
+  <si>
+    <t>-270</t>
+  </si>
+  <si>
+    <t>-219</t>
+  </si>
+  <si>
+    <t>-185</t>
+  </si>
+  <si>
+    <t>-180</t>
+  </si>
+  <si>
+    <t>+177</t>
+  </si>
+  <si>
+    <t>+300</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>53.0%</t>
+  </si>
+  <si>
+    <t>37.3%</t>
+  </si>
+  <si>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-1941</t>
-  </si>
-  <si>
-    <t>-1686</t>
-  </si>
-  <si>
-    <t>-1438</t>
-  </si>
-  <si>
-    <t>-517</t>
-  </si>
-  <si>
-    <t>-226</t>
-  </si>
-  <si>
-    <t>+226</t>
-  </si>
-  <si>
-    <t>+378</t>
-  </si>
-  <si>
-    <t>+1090</t>
-  </si>
-  <si>
-    <t>+2400</t>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-113</t>
+  </si>
+  <si>
+    <t>+168</t>
+  </si>
+  <si>
+    <t>+2122</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
   <si>
     <t>+16567</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>63.5%</t>
-  </si>
-  <si>
-    <t>20.8%</t>
-  </si>
-  <si>
-    <t>7.3%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>51.9%</t>
+  </si>
+  <si>
+    <t>44.2%</t>
   </si>
   <si>
     <t>2.2%</t>
   </si>
   <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-174</t>
-  </si>
-  <si>
-    <t>+381</t>
-  </si>
-  <si>
-    <t>+1270</t>
-  </si>
-  <si>
-    <t>+2532</t>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-108</t>
+  </si>
+  <si>
+    <t>+126</t>
   </si>
   <si>
     <t>+4445</t>
   </si>
   <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>56.2%</t>
-  </si>
-  <si>
-    <t>25.3%</t>
-  </si>
-  <si>
-    <t>12.4%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-128</t>
-  </si>
-  <si>
-    <t>+295</t>
-  </si>
-  <si>
-    <t>+706</t>
-  </si>
-  <si>
-    <t>+2757</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -608,10 +617,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -622,10 +631,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -636,10 +645,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -647,13 +656,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -661,13 +670,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,13 +684,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -689,13 +698,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -706,10 +715,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -717,13 +726,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -731,13 +740,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -745,13 +754,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -762,10 +771,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -794,30 +803,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -828,52 +837,52 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -881,83 +890,83 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -992,10 +1001,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1003,13 +1012,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1017,13 +1026,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1031,97 +1040,97 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1132,24 +1141,24 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
   <si>
     <t>Record</t>
   </si>
@@ -33,208 +33,202 @@
     <t>Little Bill</t>
   </si>
   <si>
+    <t>Philadelphia Bills Mafia</t>
+  </si>
+  <si>
+    <t>The Golden Receivers</t>
+  </si>
+  <si>
     <t>Pho_King</t>
   </si>
   <si>
-    <t>Philadelphia Bills Mafia</t>
+    <t>Lets Get Structural</t>
+  </si>
+  <si>
+    <t>J. Dobbs Holdings LLC</t>
+  </si>
+  <si>
+    <t>19th St Halal Cart</t>
   </si>
   <si>
     <t>Eli</t>
   </si>
   <si>
-    <t>19th St Halal Cart</t>
-  </si>
-  <si>
-    <t>The Golden Receivers</t>
-  </si>
-  <si>
-    <t>Lets Get Structural</t>
-  </si>
-  <si>
-    <t>J. Dobbs Holdings LLC</t>
+    <t>Cman</t>
   </si>
   <si>
     <t>Daddy's Finally Home</t>
   </si>
   <si>
-    <t>Cman</t>
-  </si>
-  <si>
     <t>Tomas</t>
   </si>
   <si>
     <t>Prahlad's Ghost</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>87.9%</t>
-  </si>
-  <si>
-    <t>80.2%</t>
-  </si>
-  <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>68.7%</t>
-  </si>
-  <si>
-    <t>64.9%</t>
-  </si>
-  <si>
-    <t>64.3%</t>
-  </si>
-  <si>
-    <t>36.1%</t>
-  </si>
-  <si>
-    <t>25.0%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>96.1%</t>
+  </si>
+  <si>
+    <t>90.9%</t>
+  </si>
+  <si>
+    <t>90.5%</t>
+  </si>
+  <si>
+    <t>88.5%</t>
+  </si>
+  <si>
+    <t>66.8%</t>
+  </si>
+  <si>
+    <t>60.3%</t>
+  </si>
+  <si>
+    <t>55.1%</t>
+  </si>
+  <si>
+    <t>41.3%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-2464</t>
+  </si>
+  <si>
+    <t>-999</t>
+  </si>
+  <si>
+    <t>-953</t>
+  </si>
+  <si>
+    <t>-770</t>
+  </si>
+  <si>
+    <t>-201</t>
+  </si>
+  <si>
+    <t>-152</t>
+  </si>
+  <si>
+    <t>-123</t>
+  </si>
+  <si>
+    <t>+142</t>
+  </si>
+  <si>
+    <t>+1036</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>81.7%</t>
+  </si>
+  <si>
+    <t>7.3%</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-446</t>
+  </si>
+  <si>
+    <t>+1270</t>
+  </si>
+  <si>
+    <t>+2464</t>
+  </si>
+  <si>
+    <t>+2532</t>
+  </si>
+  <si>
+    <t>+4067</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>50.7%</t>
+  </si>
+  <si>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>8.0%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-726</t>
-  </si>
-  <si>
-    <t>-405</t>
-  </si>
-  <si>
-    <t>-270</t>
-  </si>
-  <si>
-    <t>-219</t>
-  </si>
-  <si>
-    <t>-185</t>
-  </si>
-  <si>
-    <t>-180</t>
-  </si>
-  <si>
-    <t>+177</t>
-  </si>
-  <si>
-    <t>+300</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>-103</t>
+  </si>
+  <si>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+1150</t>
+  </si>
+  <si>
+    <t>+19900</t>
   </si>
   <si>
     <t>+33233</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>53.0%</t>
-  </si>
-  <si>
-    <t>37.3%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-113</t>
-  </si>
-  <si>
-    <t>+168</t>
-  </si>
-  <si>
-    <t>+2122</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>51.9%</t>
-  </si>
-  <si>
-    <t>44.2%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-108</t>
-  </si>
-  <si>
-    <t>+126</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -628,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -642,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -656,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
@@ -670,7 +664,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -684,7 +678,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -698,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -712,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -740,7 +734,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -768,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -803,21 +797,21 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -826,12 +820,12 @@
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -840,7 +834,7 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -848,41 +842,41 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -890,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -901,7 +895,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -910,21 +904,21 @@
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -935,10 +929,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -946,27 +940,27 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -998,13 +992,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1015,10 +1009,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1026,111 +1020,111 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1141,24 +1135,24 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -33,27 +33,27 @@
     <t>Little Bill</t>
   </si>
   <si>
+    <t>The Golden Receivers</t>
+  </si>
+  <si>
+    <t>Pho_King</t>
+  </si>
+  <si>
     <t>Philadelphia Bills Mafia</t>
   </si>
   <si>
-    <t>The Golden Receivers</t>
-  </si>
-  <si>
-    <t>Pho_King</t>
+    <t>J. Dobbs Holdings LLC</t>
   </si>
   <si>
     <t>Lets Get Structural</t>
   </si>
   <si>
-    <t>J. Dobbs Holdings LLC</t>
+    <t>Eli</t>
   </si>
   <si>
     <t>19th St Halal Cart</t>
   </si>
   <si>
-    <t>Eli</t>
-  </si>
-  <si>
     <t>Cman</t>
   </si>
   <si>
@@ -66,112 +66,109 @@
     <t>Prahlad's Ghost</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>100.0%</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>99.4%</t>
   </si>
   <si>
     <t>96.1%</t>
   </si>
   <si>
-    <t>90.9%</t>
-  </si>
-  <si>
-    <t>90.5%</t>
-  </si>
-  <si>
-    <t>88.5%</t>
-  </si>
-  <si>
-    <t>66.8%</t>
-  </si>
-  <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>55.1%</t>
-  </si>
-  <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-99900</t>
+    <t>95.1%</t>
+  </si>
+  <si>
+    <t>92.2%</t>
+  </si>
+  <si>
+    <t>89.4%</t>
+  </si>
+  <si>
+    <t>73.4%</t>
+  </si>
+  <si>
+    <t>64.4%</t>
+  </si>
+  <si>
+    <t>45.7%</t>
+  </si>
+  <si>
+    <t>28.8%</t>
+  </si>
+  <si>
+    <t>14.9%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-16567</t>
   </si>
   <si>
     <t>-2464</t>
   </si>
   <si>
-    <t>-999</t>
-  </si>
-  <si>
-    <t>-953</t>
-  </si>
-  <si>
-    <t>-770</t>
-  </si>
-  <si>
-    <t>-201</t>
-  </si>
-  <si>
-    <t>-152</t>
-  </si>
-  <si>
-    <t>-123</t>
-  </si>
-  <si>
-    <t>+142</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+8991</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-1941</t>
+  </si>
+  <si>
+    <t>-1182</t>
+  </si>
+  <si>
+    <t>-843</t>
+  </si>
+  <si>
+    <t>-276</t>
+  </si>
+  <si>
+    <t>-181</t>
+  </si>
+  <si>
+    <t>+119</t>
+  </si>
+  <si>
+    <t>+247</t>
+  </si>
+  <si>
+    <t>+571</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>81.7%</t>
-  </si>
-  <si>
-    <t>7.3%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>63.4%</t>
+  </si>
+  <si>
+    <t>12.3%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>8.0%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -180,55 +177,52 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-446</t>
-  </si>
-  <si>
-    <t>+1270</t>
-  </si>
-  <si>
-    <t>+2464</t>
-  </si>
-  <si>
-    <t>+2532</t>
-  </si>
-  <si>
-    <t>+4067</t>
-  </si>
-  <si>
-    <t>+14186</t>
+    <t>-173</t>
+  </si>
+  <si>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+1150</t>
+  </si>
+  <si>
+    <t>+1654</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>50.7%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>8.0%</t>
+    <t>54.6%</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>2.2%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-103</t>
-  </si>
-  <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+1150</t>
+    <t>-120</t>
+  </si>
+  <si>
+    <t>+137</t>
+  </si>
+  <si>
+    <t>+4445</t>
   </si>
   <si>
     <t>+19900</t>
-  </si>
-  <si>
-    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -614,7 +608,7 @@
         <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -622,13 +616,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -636,13 +630,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -650,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -670,7 +664,7 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -678,13 +672,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -698,7 +692,7 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -706,13 +700,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -726,7 +720,7 @@
         <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -734,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -748,13 +742,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -762,13 +756,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -789,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -803,66 +797,66 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -870,13 +864,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -887,10 +881,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -898,10 +892,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
@@ -912,10 +906,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -926,10 +920,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>60</v>
@@ -940,10 +934,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>60</v>
@@ -957,7 +951,7 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
@@ -981,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -992,13 +986,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1006,13 +1000,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1020,66 +1014,66 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -1087,7 +1081,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1101,13 +1095,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -1115,13 +1109,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>60</v>
@@ -1135,7 +1129,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>60</v>
@@ -1143,13 +1137,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>

--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Record</t>
   </si>
@@ -54,175 +54,169 @@
     <t>19th St Halal Cart</t>
   </si>
   <si>
+    <t>Daddy's Finally Home</t>
+  </si>
+  <si>
     <t>Cman</t>
   </si>
   <si>
-    <t>Daddy's Finally Home</t>
+    <t>Prahlad's Ghost</t>
   </si>
   <si>
     <t>Tomas</t>
   </si>
   <si>
-    <t>Prahlad's Ghost</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>96.1%</t>
-  </si>
-  <si>
-    <t>95.1%</t>
-  </si>
-  <si>
-    <t>92.2%</t>
-  </si>
-  <si>
-    <t>89.4%</t>
-  </si>
-  <si>
-    <t>73.4%</t>
-  </si>
-  <si>
-    <t>64.4%</t>
-  </si>
-  <si>
-    <t>45.7%</t>
-  </si>
-  <si>
-    <t>28.8%</t>
-  </si>
-  <si>
-    <t>14.9%</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>0-7</t>
+  </si>
+  <si>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>99.1%</t>
+  </si>
+  <si>
+    <t>97.8%</t>
+  </si>
+  <si>
+    <t>86.8%</t>
+  </si>
+  <si>
+    <t>66.0%</t>
+  </si>
+  <si>
+    <t>61.6%</t>
+  </si>
+  <si>
+    <t>41.2%</t>
+  </si>
+  <si>
+    <t>25.5%</t>
+  </si>
+  <si>
+    <t>22.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-2464</t>
-  </si>
-  <si>
-    <t>-1941</t>
-  </si>
-  <si>
-    <t>-1182</t>
-  </si>
-  <si>
-    <t>-843</t>
-  </si>
-  <si>
-    <t>-276</t>
-  </si>
-  <si>
-    <t>-181</t>
-  </si>
-  <si>
-    <t>+119</t>
-  </si>
-  <si>
-    <t>+247</t>
-  </si>
-  <si>
-    <t>+571</t>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-4445</t>
+  </si>
+  <si>
+    <t>-658</t>
+  </si>
+  <si>
+    <t>-194</t>
+  </si>
+  <si>
+    <t>-160</t>
+  </si>
+  <si>
+    <t>+143</t>
+  </si>
+  <si>
+    <t>+292</t>
+  </si>
+  <si>
+    <t>+344</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
+    <t>+99900</t>
+  </si>
+  <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>63.4%</t>
-  </si>
-  <si>
-    <t>12.3%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>8.0%</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
+    <t>56.4%</t>
+  </si>
+  <si>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>13.0%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-173</t>
-  </si>
-  <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>+1150</t>
-  </si>
-  <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>+6567</t>
+    <t>-129</t>
+  </si>
+  <si>
+    <t>+446</t>
+  </si>
+  <si>
+    <t>+669</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
   <si>
     <t>+24900</t>
   </si>
   <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>54.6%</t>
-  </si>
-  <si>
-    <t>42.2%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>-120</t>
-  </si>
-  <si>
-    <t>+137</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>59.1%</t>
+  </si>
+  <si>
+    <t>40.3%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-144</t>
+  </si>
+  <si>
+    <t>+148</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -605,10 +599,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,10 +613,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,10 +627,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -647,10 +641,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,13 +652,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -672,13 +666,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,13 +680,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,13 +694,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,13 +722,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -742,13 +736,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -756,13 +750,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -797,52 +791,52 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -850,13 +844,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -864,97 +858,97 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -986,13 +980,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1000,153 +994,153 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
+++ b/data/odds/Pennoni Younglings 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -33,12 +33,12 @@
     <t>Little Bill</t>
   </si>
   <si>
+    <t>Pho_King</t>
+  </si>
+  <si>
     <t>The Golden Receivers</t>
   </si>
   <si>
-    <t>Pho_King</t>
-  </si>
-  <si>
     <t>Philadelphia Bills Mafia</t>
   </si>
   <si>
@@ -87,136 +87,124 @@
     <t>0-7</t>
   </si>
   <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>99.1%</t>
-  </si>
-  <si>
-    <t>97.8%</t>
-  </si>
-  <si>
-    <t>86.8%</t>
-  </si>
-  <si>
-    <t>66.0%</t>
-  </si>
-  <si>
-    <t>61.6%</t>
-  </si>
-  <si>
-    <t>41.2%</t>
-  </si>
-  <si>
-    <t>25.5%</t>
-  </si>
-  <si>
-    <t>22.5%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>98.4%</t>
+  </si>
+  <si>
+    <t>86.4%</t>
+  </si>
+  <si>
+    <t>63.0%</t>
+  </si>
+  <si>
+    <t>58.5%</t>
+  </si>
+  <si>
+    <t>44.0%</t>
+  </si>
+  <si>
+    <t>27.1%</t>
+  </si>
+  <si>
+    <t>24.9%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-8991</t>
+  </si>
+  <si>
+    <t>-6150</t>
+  </si>
+  <si>
+    <t>-635</t>
+  </si>
+  <si>
+    <t>-170</t>
+  </si>
+  <si>
+    <t>-141</t>
+  </si>
+  <si>
+    <t>+127</t>
+  </si>
+  <si>
+    <t>+269</t>
+  </si>
+  <si>
+    <t>+302</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>55.8%</t>
+  </si>
+  <si>
+    <t>15.7%</t>
+  </si>
+  <si>
+    <t>13.9%</t>
+  </si>
+  <si>
+    <t>13.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>-126</t>
+  </si>
+  <si>
+    <t>+537</t>
+  </si>
+  <si>
+    <t>+619</t>
+  </si>
+  <si>
+    <t>+652</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>62.3%</t>
+  </si>
+  <si>
+    <t>36.8%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-11011</t>
-  </si>
-  <si>
-    <t>-4445</t>
-  </si>
-  <si>
-    <t>-658</t>
-  </si>
-  <si>
-    <t>-194</t>
-  </si>
-  <si>
-    <t>-160</t>
-  </si>
-  <si>
-    <t>+143</t>
-  </si>
-  <si>
-    <t>+292</t>
-  </si>
-  <si>
-    <t>+344</t>
+    <t>-165</t>
+  </si>
+  <si>
+    <t>+172</t>
+  </si>
+  <si>
+    <t>+19900</t>
   </si>
   <si>
     <t>+33233</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>56.4%</t>
-  </si>
-  <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>13.0%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-129</t>
-  </si>
-  <si>
-    <t>+446</t>
-  </si>
-  <si>
-    <t>+669</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+6150</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>59.1%</t>
-  </si>
-  <si>
-    <t>40.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-144</t>
-  </si>
-  <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -602,7 +590,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,13 +598,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,13 +612,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -641,10 +629,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -655,10 +643,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -669,10 +657,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -683,10 +671,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -697,10 +685,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -711,10 +699,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -725,10 +713,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -739,10 +727,10 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -753,10 +741,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -791,38 +779,38 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -833,10 +821,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -847,10 +835,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -861,10 +849,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -875,10 +863,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -889,10 +877,10 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -903,10 +891,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -917,10 +905,10 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -931,10 +919,10 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -945,10 +933,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -983,10 +971,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -997,150 +985,150 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
